--- a/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-data-export/inputsheet-data-export.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-data-export/inputsheet-data-export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\inputsheet-data-export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\inputsheet-data-export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22C50B0-E98C-4DD7-95E7-5C4DE7D9E541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15867098-0C2B-40A4-9F01-0C75453A6608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3550" yWindow="2480" windowWidth="20600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1610" yWindow="1910" windowWidth="22530" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inputsheet-data-export" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="64">
   <si>
     <t>■</t>
     <phoneticPr fontId="1"/>
@@ -810,6 +810,257 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>フクゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ出力実行後に、テーブル項目と入力シート項目の不一致があったことを示すアラートダイアログが表示されます。</t>
+    <rPh sb="3" eb="5">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ジッコウゴ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>フイッチ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処理結果エリアに、入力シートにはテーブルには定義されている項目「client_name_kana」が欠落していることを表示しています。</t>
+    <rPh sb="0" eb="4">
+      <t>ショリケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ケツラク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処理結果エリアに、入力シートにはテーブルには定義されている項目「start_date」と「end_date」が欠落し、かつテーブルに定義されていない項目「service_shortname」が定義されていることを表示しています。</t>
+    <rPh sb="0" eb="4">
+      <t>ショリケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ケツラク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE003_ErrorSheetExtraColumn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE004_ErrorSheetExtraAndLackColumn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE002_ExportColumnErrorDialog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE001_ExportSheetErrorDialog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ出力実行後に、出力対象テーブルと入力シート内のテーブル名に不一致があったことを示すアラートダイアログが表示されます。</t>
+    <rPh sb="3" eb="5">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ジッコウゴ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>シュツリョクタイショウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>フイッチ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値型項目への検索条件設定例</t>
+    <rPh sb="0" eb="3">
+      <t>スウチガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ケンサクジョウケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE005a_ConditionsRowForNumColumns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE005b_ConditionsRowForDateTimeColumns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日付型項目への検索条件設定例</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ケンサクジョウケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE005c_ConditionsRowForTestColumns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字型項目への検索条件設定例</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ケンサクジョウケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDE006_ConditionsByKeyOutputResult</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力対象テーブル：alltyes_test2の主キー：idの値が1以上200以下であるデータを検索した結果、200件のデータが入力シート上に出力された状態</t>
+    <rPh sb="0" eb="4">
+      <t>シュツリョクタイショウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>シュ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -907,6 +1158,1088 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7470</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>14942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>132050</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3064</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A937A40-87C3-4137-FF2C-32F376DED9C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="702235" y="1172883"/>
+          <a:ext cx="5914286" cy="3457143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54611</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>151785</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="10" name="グループ化 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FD895D2-912F-0203-AF8E-A54390FA468B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="707571" y="7937501"/>
+          <a:ext cx="13734326" cy="4460713"/>
+          <a:chOff x="704850" y="4800601"/>
+          <a:chExt cx="13681711" cy="4495185"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="図 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F350454-D975-B22E-ABE2-B1BCC0263E68}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="704850" y="4800601"/>
+            <a:ext cx="13681711" cy="4495185"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="正方形/長方形 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{001BE3C2-10A0-45EA-BFB2-10775E87A566}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="945491" y="6181532"/>
+            <a:ext cx="3335903" cy="927480"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>224119</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>47141</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>174197</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="12" name="グループ化 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1AB6649-C2AA-CAB8-FD26-396FEBBBFB5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="695833" y="13629555"/>
+          <a:ext cx="13738594" cy="4460713"/>
+          <a:chOff x="694019" y="11223812"/>
+          <a:chExt cx="13685072" cy="4495186"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="11" name="図 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4101C85-0E7A-3385-B065-4837E2071737}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="694019" y="11223812"/>
+            <a:ext cx="13685072" cy="4495186"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="正方形/長方形 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D575E074-F7CD-4C73-B2F7-4CB22E464D99}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="904359" y="12612215"/>
+            <a:ext cx="3444271" cy="942420"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>10294</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>33482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C47D803-83C0-C6A4-7878-61A13262511A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="694765" y="17137529"/>
+          <a:ext cx="5800000" cy="2580952"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>62082</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>8347</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="13" name="グループ化 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E297FC5-4E44-5AF2-2160-CC44130E66A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="715042" y="19072412"/>
+          <a:ext cx="13734326" cy="4748435"/>
+          <a:chOff x="712321" y="19224812"/>
+          <a:chExt cx="13681711" cy="4786535"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="図 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD3BAC2C-C78F-7723-A298-8FF1FBE47200}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="712321" y="19224812"/>
+            <a:ext cx="13681711" cy="4786535"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="正方形/長方形 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F25BDECD-08C7-43FA-936E-0F105DF9285C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3748367" y="20847423"/>
+            <a:ext cx="10453221" cy="1866153"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="正方形/長方形 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE87ABF-F6FE-4761-81D1-723739F24887}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="962212" y="21712518"/>
+            <a:ext cx="1008155" cy="914400"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54611</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>217523</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="18" name="グループ化 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A698834-F3F2-5248-BA50-C2C456BF3402}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="707571" y="24492857"/>
+          <a:ext cx="13734326" cy="4753237"/>
+          <a:chOff x="704850" y="24688800"/>
+          <a:chExt cx="13681711" cy="4789523"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="15" name="図 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D4B6A1B-CA37-7958-56F4-232594B1B3BE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="704850" y="24688800"/>
+            <a:ext cx="13681711" cy="4789523"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="16" name="正方形/長方形 15">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86C9B408-C53A-4C56-B2B3-A200308CCA16}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3811494" y="26296471"/>
+            <a:ext cx="6336180" cy="1866713"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="正方形/長方形 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D063912-AFEA-4F9A-BE91-D55358FAF57B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="928967" y="27163943"/>
+            <a:ext cx="1010596" cy="914435"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54611</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>62604</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="22" name="グループ化 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{017D1B03-8C32-C8D0-83B1-29E080741E60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="707571" y="29935715"/>
+          <a:ext cx="13734326" cy="4144746"/>
+          <a:chOff x="704850" y="30162501"/>
+          <a:chExt cx="13681711" cy="4177403"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="19" name="図 18">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3390011C-1255-F27E-7E93-9A3F717506FF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="704850" y="30162501"/>
+            <a:ext cx="13681711" cy="4177403"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="20" name="正方形/長方形 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BC767BE-0A26-469F-9889-E6B32E4656D8}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4168597" y="31728336"/>
+            <a:ext cx="8500401" cy="1679388"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="21" name="正方形/長方形 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A55B1035-9809-4911-8E19-FA6832C2F741}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="969682" y="32661915"/>
+            <a:ext cx="1009641" cy="753279"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54612</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>66295</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="27" name="グループ化 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25079186-C0A5-0651-E54F-04FDF6DD6859}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="707572" y="35151786"/>
+          <a:ext cx="13734326" cy="5282366"/>
+          <a:chOff x="704851" y="35413950"/>
+          <a:chExt cx="13681711" cy="5324095"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="23" name="図 22">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92F8A62C-F927-41B5-4FE0-CDC6763F5BA2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="704851" y="35413950"/>
+            <a:ext cx="13681711" cy="5324095"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="24" name="正方形/長方形 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5721155F-7085-423F-A364-44E1FD52F53E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="884143" y="37943491"/>
+            <a:ext cx="3084232" cy="236070"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="正方形/長方形 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21B170A5-055B-4F95-9ABF-B3E77E442142}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="969682" y="36882669"/>
+            <a:ext cx="3091703" cy="206188"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="26" name="正方形/長方形 25">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{887CD76F-33B8-486A-AC25-C29EA6EC1083}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2263961" y="38179562"/>
+            <a:ext cx="11960039" cy="2042458"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -7827,116 +9160,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
-  <dimension ref="B3:CD573"/>
+  <dimension ref="B1:CD579"/>
   <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="3.08203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="CD3" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="2"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="2"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="2"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="2"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="2"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="2"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="2"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B168" s="2"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B183" s="2"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B236" s="2"/>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B249" s="2"/>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B258" s="2"/>
-    </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B277" s="2"/>
-    </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B289" s="2"/>
-    </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B301" s="2"/>
-    </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B330" s="2"/>
-    </row>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B333" s="3"/>
-    </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B365" s="2"/>
-    </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B383" s="2"/>
-    </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B384" s="2"/>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B410" s="2"/>
-    </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B419" s="2"/>
-    </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B436" s="2"/>
-    </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B469" s="2"/>
-    </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B511" s="2"/>
-    </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B538" s="2"/>
-    </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B573" s="2"/>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="2"/>
+      <c r="D17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN17" s="2"/>
+      <c r="CD17" s="2"/>
+    </row>
+    <row r="34" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="2"/>
+      <c r="D35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN35" s="2"/>
+      <c r="CD35" s="2"/>
+    </row>
+    <row r="45" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="2"/>
+    </row>
+    <row r="54" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="2"/>
+    </row>
+    <row r="58" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="59" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="2"/>
+      <c r="D59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN59" s="2"/>
+      <c r="CD59" s="2"/>
+    </row>
+    <row r="83" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="2"/>
+      <c r="D84" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN84" s="2"/>
+      <c r="CD84" s="2"/>
+    </row>
+    <row r="88" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="2"/>
+    </row>
+    <row r="98" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="2"/>
+    </row>
+    <row r="107" spans="2:82" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="2"/>
+      <c r="D108" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AN108" s="2"/>
+      <c r="CD108" s="2"/>
+    </row>
+    <row r="112" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="2"/>
+    </row>
+    <row r="131" spans="2:82" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="2"/>
+      <c r="D132" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN132" s="2"/>
+      <c r="CD132" s="2"/>
+    </row>
+    <row r="136" spans="2:82" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="2"/>
+    </row>
+    <row r="151" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B151" s="2"/>
+    </row>
+    <row r="153" spans="2:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B153" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C154" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B170" s="2"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B174" s="2"/>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B189" s="2"/>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B209" s="2"/>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B228" s="2"/>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B242" s="2"/>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B255" s="2"/>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B264" s="2"/>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B283" s="2"/>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B295" s="2"/>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B307" s="2"/>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B336" s="2"/>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B339" s="3"/>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B362" s="2"/>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B371" s="2"/>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B389" s="2"/>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B390" s="2"/>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B416" s="2"/>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B425" s="2"/>
+    </row>
+    <row r="442" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B442" s="2"/>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B475" s="2"/>
+    </row>
+    <row r="517" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B517" s="2"/>
+    </row>
+    <row r="544" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B544" s="2"/>
+    </row>
+    <row r="579" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B579" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
